--- a/artfynd/A 54697-2025 artfynd.xlsx
+++ b/artfynd/A 54697-2025 artfynd.xlsx
@@ -1063,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133398693</v>
+        <v>133398563</v>
       </c>
       <c r="B6" t="n">
-        <v>80438</v>
+        <v>80467</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>590441</v>
+        <v>590439</v>
       </c>
       <c r="R6" t="n">
-        <v>7001850</v>
+        <v>7001858</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1128,12 +1128,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-06-18</t>
+          <t>2024-06-24</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-06-18</t>
+          <t>2024-06-24</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1160,32 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133398563</v>
+        <v>133398693</v>
       </c>
       <c r="B7" t="n">
-        <v>80467</v>
+        <v>80438</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>590439</v>
+        <v>590441</v>
       </c>
       <c r="R7" t="n">
-        <v>7001858</v>
+        <v>7001850</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1225,12 +1225,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-06-24</t>
+          <t>2024-06-18</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-06-24</t>
+          <t>2024-06-18</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 54697-2025 artfynd.xlsx
+++ b/artfynd/A 54697-2025 artfynd.xlsx
@@ -1063,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133398563</v>
+        <v>133398693</v>
       </c>
       <c r="B6" t="n">
-        <v>80467</v>
+        <v>80438</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>590439</v>
+        <v>590441</v>
       </c>
       <c r="R6" t="n">
-        <v>7001858</v>
+        <v>7001850</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1128,12 +1128,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-06-24</t>
+          <t>2024-06-18</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-06-24</t>
+          <t>2024-06-18</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1160,32 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133398693</v>
+        <v>133398563</v>
       </c>
       <c r="B7" t="n">
-        <v>80438</v>
+        <v>80467</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>590441</v>
+        <v>590439</v>
       </c>
       <c r="R7" t="n">
-        <v>7001850</v>
+        <v>7001858</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1225,12 +1225,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-06-18</t>
+          <t>2024-06-24</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-06-18</t>
+          <t>2024-06-24</t>
         </is>
       </c>
       <c r="AD7" t="b">
